--- a/excel-files/CALOOCAN/HORACIO DELA COSTA ELEMENTARY SCHOOL.xlsx
+++ b/excel-files/CALOOCAN/HORACIO DELA COSTA ELEMENTARY SCHOOL.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29704"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29816"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jonathan Buquia\Downloads\OFFICE\SEMINARS\Workshop on the Strengthened Regional Inventory of Learning Resources\SCHOOLS in NCR\CALOOCAN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="188" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{150CD0BE-198E-41CD-8C87-0F08BB727837}"/>
+  <xr:revisionPtr revIDLastSave="224" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{45E3795C-B5BD-4397-9C42-EE7D006E9EFF}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TextBooks" sheetId="1" r:id="rId1"/>
@@ -764,7 +764,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="63">
+  <dxfs count="90">
     <dxf>
       <font>
         <b/>
@@ -1926,6 +1926,41 @@
         </patternFill>
       </fill>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="15"/>
+        <color theme="1"/>
+        <name val="Bookman Old Style"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left/>
         <right style="thin">
@@ -1965,6 +2000,41 @@
         </patternFill>
       </fill>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="15"/>
+        <color theme="1"/>
+        <name val="Bookman Old Style"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left/>
         <right style="thin">
@@ -2004,6 +2074,41 @@
         </patternFill>
       </fill>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="15"/>
+        <color theme="1"/>
+        <name val="Bookman Old Style"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color rgb="FF000000"/>
@@ -2045,6 +2150,43 @@
         </patternFill>
       </fill>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="15"/>
+        <color theme="1"/>
+        <name val="Bookman Old Style"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left/>
         <right style="thin">
@@ -2084,6 +2226,41 @@
         </patternFill>
       </fill>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="15"/>
+        <color theme="1"/>
+        <name val="Bookman Old Style"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left/>
         <right style="thin">
@@ -2123,6 +2300,41 @@
         </patternFill>
       </fill>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="15"/>
+        <color theme="1"/>
+        <name val="Bookman Old Style"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left/>
         <right style="thin">
@@ -2162,6 +2374,41 @@
         </patternFill>
       </fill>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="15"/>
+        <color theme="1"/>
+        <name val="Bookman Old Style"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left/>
         <right style="thin">
@@ -2201,6 +2448,41 @@
         </patternFill>
       </fill>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="15"/>
+        <color theme="1"/>
+        <name val="Bookman Old Style"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left/>
         <right style="thin">
@@ -2240,6 +2522,41 @@
         </patternFill>
       </fill>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="15"/>
+        <color theme="1"/>
+        <name val="Bookman Old Style"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color rgb="FF000000"/>
@@ -2281,6 +2598,43 @@
         </patternFill>
       </fill>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="15"/>
+        <color theme="1"/>
+        <name val="Bookman Old Style"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left/>
         <right style="thin">
@@ -2320,6 +2674,41 @@
         </patternFill>
       </fill>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="15"/>
+        <color theme="1"/>
+        <name val="Bookman Old Style"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left/>
         <right style="thin">
@@ -2359,6 +2748,41 @@
         </patternFill>
       </fill>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="15"/>
+        <color theme="1"/>
+        <name val="Bookman Old Style"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left/>
         <right style="thin">
@@ -2398,6 +2822,41 @@
         </patternFill>
       </fill>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="15"/>
+        <color theme="1"/>
+        <name val="Bookman Old Style"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left/>
         <right style="thin">
@@ -2437,6 +2896,41 @@
         </patternFill>
       </fill>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="15"/>
+        <color theme="1"/>
+        <name val="Bookman Old Style"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left/>
         <right style="thin">
@@ -2476,6 +2970,41 @@
         </patternFill>
       </fill>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="15"/>
+        <color theme="1"/>
+        <name val="Bookman Old Style"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color rgb="FF000000"/>
@@ -2517,6 +3046,43 @@
         </patternFill>
       </fill>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="15"/>
+        <color theme="1"/>
+        <name val="Bookman Old Style"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left/>
         <right style="thin">
@@ -2549,6 +3115,116 @@
         <charset val="134"/>
         <scheme val="none"/>
       </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="15"/>
+        <color theme="1"/>
+        <name val="Bookman Old Style"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="15"/>
+        <color theme="1"/>
+        <name val="Bookman Old Style"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="15"/>
+        <color theme="1"/>
+        <name val="Bookman Old Style"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
       <fill>
         <patternFill patternType="solid">
           <fgColor indexed="64"/>
@@ -2596,6 +3272,42 @@
         </patternFill>
       </fill>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="15"/>
+        <color theme="1"/>
+        <name val="Bookman Old Style"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left/>
         <right style="thin">
@@ -2636,6 +3348,41 @@
         </patternFill>
       </fill>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="15"/>
+        <color theme="1"/>
+        <name val="Bookman Old Style"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left/>
         <right style="thin">
@@ -2675,8 +3422,45 @@
         </patternFill>
       </fill>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="15"/>
+        <color theme="1"/>
+        <name val="Bookman Old Style"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
-        <left/>
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
         <right style="thin">
           <color rgb="FF000000"/>
         </right>
@@ -2714,10 +3498,45 @@
         </patternFill>
       </fill>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="15"/>
+        <color theme="1"/>
+        <name val="Bookman Old Style"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
+        <left/>
         <right style="thin">
           <color rgb="FF000000"/>
         </right>
@@ -2755,6 +3574,41 @@
         </patternFill>
       </fill>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="15"/>
+        <color theme="1"/>
+        <name val="Bookman Old Style"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left/>
         <right style="thin">
@@ -2794,8 +3648,45 @@
         </patternFill>
       </fill>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="15"/>
+        <color theme="1"/>
+        <name val="Bookman Old Style"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
-        <left/>
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
         <right style="thin">
           <color rgb="FF000000"/>
         </right>
@@ -2833,6 +3724,43 @@
         </patternFill>
       </fill>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="15"/>
+        <color theme="1"/>
+        <name val="Bookman Old Style"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color rgb="FF000000"/>
@@ -2874,6 +3802,43 @@
         </patternFill>
       </fill>
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="15"/>
+        <color theme="1"/>
+        <name val="Bookman Old Style"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color rgb="FF000000"/>
@@ -2915,7 +3880,7 @@
         </patternFill>
       </fill>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
+      <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color rgb="FF000000"/>
         </left>
@@ -2925,11 +3890,7 @@
         <top style="thin">
           <color rgb="FF000000"/>
         </top>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
+        <bottom/>
       </border>
     </dxf>
     <dxf>
@@ -3025,7 +3986,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{DC451CB5-2E69-4EAA-94B0-458F89F93F29}" name="Table2" displayName="Table2" ref="A1:H145" totalsRowShown="0" headerRowDxfId="62" headerRowBorderDxfId="60" tableBorderDxfId="61">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{DC451CB5-2E69-4EAA-94B0-458F89F93F29}" name="Table2" displayName="Table2" ref="A1:H145" totalsRowShown="0" headerRowDxfId="89" headerRowBorderDxfId="87" tableBorderDxfId="88">
   <autoFilter ref="A1:H145" xr:uid="{DC451CB5-2E69-4EAA-94B0-458F89F93F29}"/>
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{6C961029-0F4E-47F8-B820-C81BD075C863}" name="Grade Level"/>
@@ -3042,54 +4003,54 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D7C37D80-F2E1-4395-8B6C-0FD477B4D8F8}" name="Table1" displayName="Table1" ref="A2:AA127" totalsRowShown="0" dataDxfId="59" headerRowBorderDxfId="57" tableBorderDxfId="58">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D7C37D80-F2E1-4395-8B6C-0FD477B4D8F8}" name="Table1" displayName="Table1" ref="A2:AA127" totalsRowShown="0" dataDxfId="86" headerRowBorderDxfId="84" tableBorderDxfId="85">
   <autoFilter ref="A2:AA127" xr:uid="{D7C37D80-F2E1-4395-8B6C-0FD477B4D8F8}"/>
   <tableColumns count="27">
-    <tableColumn id="1" xr3:uid="{451CCD6B-9C4E-44A3-945A-DE807169F46B}" name="Grade Level" dataDxfId="56"/>
-    <tableColumn id="2" xr3:uid="{C6CCCB1C-6639-4C28-A4BA-B187B2F73B59}" name="SUBJECTS" dataDxfId="55"/>
-    <tableColumn id="3" xr3:uid="{945324E6-140A-476C-A8C3-23A16D4D262F}" name="Enrolment S.Y. 2025-2026 " dataDxfId="54"/>
-    <tableColumn id="4" xr3:uid="{A2D4C0AF-3699-4D3C-A791-2D7D8004CC89}" name="Quantity based on Target LAS - Q1 " dataDxfId="53">
+    <tableColumn id="1" xr3:uid="{451CCD6B-9C4E-44A3-945A-DE807169F46B}" name="Grade Level" dataDxfId="82" totalsRowDxfId="83"/>
+    <tableColumn id="2" xr3:uid="{C6CCCB1C-6639-4C28-A4BA-B187B2F73B59}" name="SUBJECTS" dataDxfId="80" totalsRowDxfId="81"/>
+    <tableColumn id="3" xr3:uid="{945324E6-140A-476C-A8C3-23A16D4D262F}" name="Enrolment S.Y. 2025-2026 " dataDxfId="78" totalsRowDxfId="79"/>
+    <tableColumn id="4" xr3:uid="{A2D4C0AF-3699-4D3C-A791-2D7D8004CC89}" name="Quantity based on Target LAS - Q1 " dataDxfId="76" totalsRowDxfId="77">
       <calculatedColumnFormula>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{9CE2D7B1-8761-49A3-A313-E7834B16687D}" name="Quantity of Learning Activity Sheets Received (Quantity received x No. of LAS) - Q1" dataDxfId="52"/>
-    <tableColumn id="6" xr3:uid="{FCD520AB-D938-4542-9B56-AEC07AB5F1DC}" name="Year of Delivery-LAS - Q1" dataDxfId="51"/>
-    <tableColumn id="7" xr3:uid="{674474DE-9D20-41C1-8261-DA9C4A95671C}" name="SOURCE - LAS (CO,RO, SDO) - Q1" dataDxfId="50"/>
-    <tableColumn id="8" xr3:uid="{58D9CB98-8F6F-4F61-9103-C27B8FFBDB51}" name="GAP - LAS - Q1" dataDxfId="49">
+    <tableColumn id="5" xr3:uid="{9CE2D7B1-8761-49A3-A313-E7834B16687D}" name="Quantity of Learning Activity Sheets Received (Quantity received x No. of LAS) - Q1" dataDxfId="74" totalsRowDxfId="75"/>
+    <tableColumn id="6" xr3:uid="{FCD520AB-D938-4542-9B56-AEC07AB5F1DC}" name="Year of Delivery-LAS - Q1" dataDxfId="72" totalsRowDxfId="73"/>
+    <tableColumn id="7" xr3:uid="{674474DE-9D20-41C1-8261-DA9C4A95671C}" name="SOURCE - LAS (CO,RO, SDO) - Q1" dataDxfId="70" totalsRowDxfId="71"/>
+    <tableColumn id="8" xr3:uid="{58D9CB98-8F6F-4F61-9103-C27B8FFBDB51}" name="GAP - LAS - Q1" dataDxfId="68" totalsRowDxfId="69">
       <calculatedColumnFormula>IF((D3-E3)&lt;0,0,(D3-E3))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{E6406FC4-4491-4FD6-9EA2-F088E94C44F4}" name="SURPLUS - LAS - Q1" dataDxfId="48">
+    <tableColumn id="9" xr3:uid="{E6406FC4-4491-4FD6-9EA2-F088E94C44F4}" name="SURPLUS - LAS - Q1" dataDxfId="66" totalsRowDxfId="67">
       <calculatedColumnFormula>IF((E3-D3)&lt;0,0,(E3-D3))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{1E56D889-DC27-4BCB-B61E-06BBBE734949}" name="Quantity based on Target LAS - Q2" dataDxfId="47">
+    <tableColumn id="10" xr3:uid="{1E56D889-DC27-4BCB-B61E-06BBBE734949}" name="Quantity based on Target LAS - Q2" dataDxfId="64" totalsRowDxfId="65">
       <calculatedColumnFormula>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{E933BF99-834C-4F15-8181-7D005013BD85}" name="Quantity of Learning Activity Sheets Received (Quantity received x No. of LAS) Q2" dataDxfId="46"/>
-    <tableColumn id="12" xr3:uid="{F2E2CB95-E0BD-4C6E-ACFE-F201177004A0}" name="Year of Delivery-LAS Q2" dataDxfId="45"/>
-    <tableColumn id="13" xr3:uid="{163FBFFB-0AB7-44C8-89C4-72AA64C1EAC7}" name="SOURCE-LAS (CO,RO, SDO) Q2" dataDxfId="44"/>
-    <tableColumn id="14" xr3:uid="{EACC05A8-C68D-4495-BC08-73F093C4992F}" name="GAP - LAS -Q2" dataDxfId="43"/>
-    <tableColumn id="15" xr3:uid="{28A44E24-3E28-4B7F-BADE-28BB84F0B810}" name="SURPLUS - LAS -Q2" dataDxfId="42"/>
-    <tableColumn id="16" xr3:uid="{87878677-5715-46B6-9BA9-9D08DE9A3335}" name="Quantity based on Target LAS - Q3" dataDxfId="41">
+    <tableColumn id="11" xr3:uid="{E933BF99-834C-4F15-8181-7D005013BD85}" name="Quantity of Learning Activity Sheets Received (Quantity received x No. of LAS) Q2" dataDxfId="62" totalsRowDxfId="63"/>
+    <tableColumn id="12" xr3:uid="{F2E2CB95-E0BD-4C6E-ACFE-F201177004A0}" name="Year of Delivery-LAS Q2" dataDxfId="60" totalsRowDxfId="61"/>
+    <tableColumn id="13" xr3:uid="{163FBFFB-0AB7-44C8-89C4-72AA64C1EAC7}" name="SOURCE-LAS (CO,RO, SDO) Q2" dataDxfId="58" totalsRowDxfId="59"/>
+    <tableColumn id="14" xr3:uid="{EACC05A8-C68D-4495-BC08-73F093C4992F}" name="GAP - LAS -Q2" dataDxfId="56" totalsRowDxfId="57"/>
+    <tableColumn id="15" xr3:uid="{28A44E24-3E28-4B7F-BADE-28BB84F0B810}" name="SURPLUS - LAS -Q2" dataDxfId="54" totalsRowDxfId="55"/>
+    <tableColumn id="16" xr3:uid="{87878677-5715-46B6-9BA9-9D08DE9A3335}" name="Quantity based on Target LAS - Q3" dataDxfId="52" totalsRowDxfId="53">
       <calculatedColumnFormula>#REF!*8</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="17" xr3:uid="{48667A1F-77B1-47A6-83F7-61ED15F61DDB}" name="Quantity of Learning Activity Sheets Received (Quantity received x No. of LAS) - Q3" dataDxfId="40"/>
-    <tableColumn id="18" xr3:uid="{56F2625D-2CEE-478E-A8DE-42A7191C3835}" name="Year of Delivery-LAS - Q3" dataDxfId="39"/>
-    <tableColumn id="19" xr3:uid="{EF0F614F-5FED-4639-8798-840D9677B8DA}" name="SOURCE-LAS (CO,RO, SDO) - Q3" dataDxfId="38"/>
-    <tableColumn id="20" xr3:uid="{FD91DDEE-DBA8-4E2C-94B2-23AE9F73CC4A}" name="GAP - LAS - Q3" dataDxfId="37">
+    <tableColumn id="17" xr3:uid="{48667A1F-77B1-47A6-83F7-61ED15F61DDB}" name="Quantity of Learning Activity Sheets Received (Quantity received x No. of LAS) - Q3" dataDxfId="50" totalsRowDxfId="51"/>
+    <tableColumn id="18" xr3:uid="{56F2625D-2CEE-478E-A8DE-42A7191C3835}" name="Year of Delivery-LAS - Q3" dataDxfId="48" totalsRowDxfId="49"/>
+    <tableColumn id="19" xr3:uid="{EF0F614F-5FED-4639-8798-840D9677B8DA}" name="SOURCE-LAS (CO,RO, SDO) - Q3" dataDxfId="46" totalsRowDxfId="47"/>
+    <tableColumn id="20" xr3:uid="{FD91DDEE-DBA8-4E2C-94B2-23AE9F73CC4A}" name="GAP - LAS - Q3" dataDxfId="44" totalsRowDxfId="45">
       <calculatedColumnFormula>IF((P3-Q3)&lt;0,0,(P3-Q3))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="21" xr3:uid="{DB598C6C-E489-4B0F-9BC6-B0981F7D2582}" name="SURPLUS - LAS - Q3" dataDxfId="36">
+    <tableColumn id="21" xr3:uid="{DB598C6C-E489-4B0F-9BC6-B0981F7D2582}" name="SURPLUS - LAS - Q3" dataDxfId="42" totalsRowDxfId="43">
       <calculatedColumnFormula>IF((Q3-P3)&lt;0,0,(Q3-P3))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="22" xr3:uid="{8CD6906A-7980-46E8-80B2-8563AEBC71F7}" name="Quantity based on Target LAS - Q4" dataDxfId="35">
+    <tableColumn id="22" xr3:uid="{8CD6906A-7980-46E8-80B2-8563AEBC71F7}" name="Quantity based on Target LAS - Q4" dataDxfId="40" totalsRowDxfId="41">
       <calculatedColumnFormula>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="23" xr3:uid="{6287B1E4-D2AD-47C7-BD86-3391F339B1E3}" name="Quantity of Learning Activity Sheets Received (Quantity received x No. of LAS)- Q4" dataDxfId="34"/>
-    <tableColumn id="24" xr3:uid="{205BCDBA-0424-492C-B4EF-841B8A3A1521}" name="Year of Delivery - LAS - Q4" dataDxfId="33"/>
-    <tableColumn id="25" xr3:uid="{8226E35B-1F3B-4D2A-815B-9D4C0A24EE7E}" name="SOURCE - LAS (CO,RO, SDO) - Q4" dataDxfId="32"/>
-    <tableColumn id="26" xr3:uid="{5B37A4B7-CD16-4D9A-8A47-D9EA73F613BC}" name="GAP - LAS - Q4" dataDxfId="31">
+    <tableColumn id="23" xr3:uid="{6287B1E4-D2AD-47C7-BD86-3391F339B1E3}" name="Quantity of Learning Activity Sheets Received (Quantity received x No. of LAS)- Q4" dataDxfId="38" totalsRowDxfId="39"/>
+    <tableColumn id="24" xr3:uid="{205BCDBA-0424-492C-B4EF-841B8A3A1521}" name="Year of Delivery - LAS - Q4" dataDxfId="36" totalsRowDxfId="37"/>
+    <tableColumn id="25" xr3:uid="{8226E35B-1F3B-4D2A-815B-9D4C0A24EE7E}" name="SOURCE - LAS (CO,RO, SDO) - Q4" dataDxfId="34" totalsRowDxfId="35"/>
+    <tableColumn id="26" xr3:uid="{5B37A4B7-CD16-4D9A-8A47-D9EA73F613BC}" name="GAP - LAS - Q4" dataDxfId="32" totalsRowDxfId="33">
       <calculatedColumnFormula>IF((V3-W3)&lt;0,0,(V3-W3))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="27" xr3:uid="{38E9C5F3-3FF5-4B13-A9DA-0081A90F35C5}" name="SURPLUS - LAS - Q4" dataDxfId="30">
+    <tableColumn id="27" xr3:uid="{38E9C5F3-3FF5-4B13-A9DA-0081A90F35C5}" name="SURPLUS - LAS - Q4" dataDxfId="30" totalsRowDxfId="31">
       <calculatedColumnFormula>IF((W3-V3)&lt;0,0,(W3-V3))</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5568,8 +6529,8 @@
   </protectedRanges>
   <phoneticPr fontId="8" type="noConversion"/>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E14:E19 E21:E29 E91:E98 E51:E59 E61:E69 E41:E49 E2:E6 E71:E79 E81:E89 E8:E12 E31:E39" xr:uid="{B46E7B13-721E-4D49-837E-C02BF9777D48}">
-      <formula1>"2024,2025"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E91:E98 E81:E89 E71:E79 E61:E69 E51:E59 E41:E49 E31:E39 E21:E29 E14:E19 E8:E12 E2:E6" xr:uid="{B46E7B13-721E-4D49-837E-C02BF9777D48}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F14:F19 F21:F29 F31:F39 F41:F49 F51:F59 F61:F69 F71:F79 F81:F89 F2:F6 F8:F12 F91:F98" xr:uid="{2F7388E0-D1A1-4571-8C10-96CB9A727EB3}">
       <formula1>"CO,RO,SDO"</formula1>
@@ -10280,7 +11241,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:27" ht="19.149999999999999">
+    <row r="71" spans="1:27" ht="19.5">
       <c r="A71" s="10">
         <v>7</v>
       </c>
@@ -10915,7 +11876,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:27" ht="19.149999999999999">
+    <row r="81" spans="1:27" ht="19.5">
       <c r="A81" s="10">
         <v>8</v>
       </c>
@@ -11550,7 +12511,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:27" ht="19.149999999999999">
+    <row r="91" spans="1:27" ht="19.5">
       <c r="A91" s="10">
         <v>9</v>
       </c>
@@ -12185,7 +13146,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:27" ht="19.149999999999999">
+    <row r="101" spans="1:27" ht="19.5">
       <c r="A101" s="10">
         <v>10</v>
       </c>
@@ -12751,7 +13712,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:27" ht="38.450000000000003">
+    <row r="110" spans="1:27" ht="38.25">
       <c r="A110" s="1" t="s">
         <v>24</v>
       </c>
@@ -12831,7 +13792,7 @@
       <c r="Z111" s="13"/>
       <c r="AA111" s="13"/>
     </row>
-    <row r="112" spans="1:27" ht="19.149999999999999">
+    <row r="112" spans="1:27" ht="19.5">
       <c r="A112" s="1"/>
       <c r="B112" s="9"/>
       <c r="C112" s="1"/>
@@ -13451,7 +14412,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:27" ht="19.149999999999999">
+    <row r="122" spans="1:27" ht="19.5">
       <c r="A122" s="1"/>
       <c r="B122" s="9"/>
       <c r="C122" s="1"/>
@@ -13637,7 +14598,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="125" spans="1:27" ht="19.149999999999999">
+    <row r="125" spans="1:27" ht="19.5">
       <c r="A125" s="1"/>
       <c r="B125" s="9"/>
       <c r="C125" s="1"/>
@@ -13699,7 +14660,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="126" spans="1:27" ht="19.149999999999999">
+    <row r="126" spans="1:27" ht="19.5">
       <c r="A126" s="1"/>
       <c r="B126" s="9"/>
       <c r="C126" s="1"/>
@@ -13761,7 +14722,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="127" spans="1:27" ht="19.149999999999999">
+    <row r="127" spans="1:27" ht="19.5">
       <c r="A127" s="29"/>
       <c r="B127" s="30"/>
       <c r="C127" s="29"/>
@@ -13820,186 +14781,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="1:27">
-      <c r="J128" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="129" spans="10:10">
-      <c r="J129" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="130" spans="10:10">
-      <c r="J130" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="131" spans="10:10">
-      <c r="J131" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="132" spans="10:10">
-      <c r="J132" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="133" spans="10:10">
-      <c r="J133" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="134" spans="10:10">
-      <c r="J134" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="135" spans="10:10">
-      <c r="J135" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="136" spans="10:10">
-      <c r="J136" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="137" spans="10:10">
-      <c r="J137" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="138" spans="10:10">
-      <c r="J138" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="139" spans="10:10">
-      <c r="J139" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="140" spans="10:10">
-      <c r="J140" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="141" spans="10:10">
-      <c r="J141" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="142" spans="10:10">
-      <c r="J142" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="143" spans="10:10">
-      <c r="J143" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="144" spans="10:10">
-      <c r="J144" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="145" spans="10:10">
-      <c r="J145" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="146" spans="10:10">
-      <c r="J146" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="147" spans="10:10">
-      <c r="J147" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="148" spans="10:10">
-      <c r="J148" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="149" spans="10:10">
-      <c r="J149" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="150" spans="10:10">
-      <c r="J150" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="151" spans="10:10">
-      <c r="J151" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="152" spans="10:10">
-      <c r="J152" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="153" spans="10:10">
-      <c r="J153" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="154" spans="10:10">
-      <c r="J154" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="155" spans="10:10">
-      <c r="J155" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="156" spans="10:10">
-      <c r="J156" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="157" spans="10:10">
-      <c r="J157" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
+    <row r="157" ht="15"/>
   </sheetData>
   <protectedRanges>
     <protectedRange sqref="C2:C3 C63:C71 C73:C81 C83:C91 C93:C101 C103:C110 C112:C127 C33:C41 C43:C51 C53:C61" name="Textbooks"/>
@@ -14016,15 +14798,18 @@
     <mergeCell ref="P1:U1"/>
     <mergeCell ref="V1:AA1"/>
   </mergeCells>
-  <dataValidations count="3">
+  <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S112:S127 M112:M127 Y112:Y127 G112:G127" xr:uid="{8289B4A9-982E-4C7E-A8E2-4BF3404561DB}">
       <formula1>"CO,RO,SDO"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X23:X31 X33:X41 X43:X51 X63:X71 X73:X81 X53:X61 L112:L127 X83:X91 X93:X101 X14:X21 X5:X12 L23:L31 L33:L41 L43:L51 L63:L71 L73:L81 L53:L61 R112:R127 L83:L91 L93:L101 L14:L21 L5:L12 R23:R31 R33:R41 R43:R51 R63:R71 R73:R81 R53:R61 F112:F127 R83:R91 R93:R101 R14:R21 R5:R12 F14:F21 F33:F41 F23:F31 F63:F71 F73:F81 F53:F61 F5:F12 F83:F91 F93:F101 X112:X127 F103:F110 R103:R110 L103:L110 X103:X110 F43:F51" xr:uid="{4ECCD083-8EC4-42EE-B46C-B614411F330D}">
-      <formula1>"2024,2025"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X112:X127 X103:X110 X93:X101 X83:X91 X73:X81 X63:X71 X53:X61 X43:X51 X33:X41 X23:X31 X14:X21 X5:X12" xr:uid="{4ECCD083-8EC4-42EE-B46C-B614411F330D}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M14:M110 Y14:Y110 S4:S110 G5:G12 M5:M12 Y5:Y12 G103:G110 G14:G21 G33:G41 G23:G31 G53:G61 G63:G71 G73:G81 G83:G91 G93:G101 G43:G51" xr:uid="{5129D80C-83DF-45BE-B6AD-F21CA596CBA5}">
       <formula1>"CO,RO,SDO,LGU,SCHOOL"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F112:F127 F103:F110 F93:F101 F83:F91 F73:F81 F63:F71 F53:F61 F43:F51 F33:F41 F23:F31 F14:F21 F5:F12 L112:L127 L103:L110 L93:L101 L83:L91 L73:L81 L63:L71 L53:L61 L43:L51 L33:L41 L23:L31 L14:L21 L5:L12 R112:R127 R103:R110 R93:R101 R83:R91 R73:R81 R63:R71 R53:R61 R43:R51 R33:R41 R23:R31 R14:R21 R5:R12" xr:uid="{937DD024-763F-4463-BA49-D4164B9650B3}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -14039,7 +14824,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F176E3C0-9A94-45E4-9AFD-70DF8ABE5E5A}">
-  <dimension ref="A1:AB170"/>
+  <dimension ref="A1:AB140"/>
   <sheetFormatPr defaultRowHeight="13.9"/>
   <cols>
     <col min="1" max="1" width="9.42578125" customWidth="1"/>
@@ -22568,186 +23353,6 @@
       <c r="AA140" s="7"/>
       <c r="AB140" s="7"/>
     </row>
-    <row r="141" spans="1:28">
-      <c r="J141" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="142" spans="1:28">
-      <c r="J142" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="143" spans="1:28">
-      <c r="J143" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="144" spans="1:28">
-      <c r="J144" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="145" spans="10:10">
-      <c r="J145" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="146" spans="10:10">
-      <c r="J146" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="147" spans="10:10">
-      <c r="J147" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="148" spans="10:10">
-      <c r="J148" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="149" spans="10:10">
-      <c r="J149" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="150" spans="10:10">
-      <c r="J150" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="151" spans="10:10">
-      <c r="J151" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="152" spans="10:10">
-      <c r="J152" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="153" spans="10:10">
-      <c r="J153" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="154" spans="10:10">
-      <c r="J154" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="155" spans="10:10">
-      <c r="J155" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="156" spans="10:10">
-      <c r="J156" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="157" spans="10:10">
-      <c r="J157" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="158" spans="10:10">
-      <c r="J158" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="159" spans="10:10">
-      <c r="J159" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="160" spans="10:10">
-      <c r="J160" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="161" spans="10:10">
-      <c r="J161" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="162" spans="10:10">
-      <c r="J162" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="163" spans="10:10">
-      <c r="J163" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="164" spans="10:10">
-      <c r="J164" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="165" spans="10:10">
-      <c r="J165" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="166" spans="10:10">
-      <c r="J166" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="167" spans="10:10">
-      <c r="J167" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="168" spans="10:10">
-      <c r="J168" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="169" spans="10:10">
-      <c r="J169" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="170" spans="10:10">
-      <c r="J170" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
   </sheetData>
   <protectedRanges>
     <protectedRange sqref="C12:C19 C67:C77 C79:C89 C115:C122 C103:C113 C91:C101 C2:C10 C21:C29 C31:C41 C43:C53 C55:C65" name="Textbooks"/>
@@ -22761,12 +23366,15 @@
     <mergeCell ref="P1:U1"/>
     <mergeCell ref="V1:AA1"/>
   </mergeCells>
-  <dataValidations count="2">
+  <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S115:S122 Y115:Y122 G115:G122 Y3:Y10 S3:S10 M3:M10 G3:G10 G12:G19 Y12:Y19 S12:S19 M12:M19 M21:M29 G21:G29 Y21:Y29 S21:S29 S31:S41 M31:M41 G31:G41 Y31:Y41 Y43:Y53 S43:S53 M43:M53 G43:G53 M115:M122 S55:S65 M55:M65 G55:G65 M67:M77 G67:G77 Y67:Y77 S67:S77 S79:S89 M79:M89 G79:G89 Y79:Y89 Y91:Y101 S91:S101 M91:M101 G91:G101 G103:G113 Y103:Y113 S103:S113 M103:M113 Y55:Y65" xr:uid="{CBD486C7-A5DB-48F1-B496-5027CC51E830}">
       <formula1>"CO,RO,SDO,LGU,SCHOOL"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X21:X29 X31:X41 X43:X53 X67:X77 X79:X89 R55:R65 X91:X101 X103:X113 X12:X19 X3:X10 L21:L29 L31:L41 L43:L53 L67:L77 L79:L89 F55:F65 L91:L101 L103:L113 L12:L19 L3:L10 R21:R29 R31:R41 R43:R53 R67:R77 R79:R89 L55:L65 R91:R101 R103:R113 R12:R19 R3:R10 F21:F29 F31:F41 F43:F53 F67:F77 F79:F89 F103:F113 F3:F10 F91:F101 X115:X122 F12:F19 F115:F122 R115:R122 L115:L122 X55:X65" xr:uid="{77F72D89-8371-4D0C-A323-BD25723C617C}">
-      <formula1>"2024,2025"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X115:X122 X103:X113 X91:X101 X79:X89 X67:X77 X55:X65 X43:X53 X31:X41 X21:X29 X12:X19 X3:X10" xr:uid="{77F72D89-8371-4D0C-A323-BD25723C617C}">
+      <formula1>"2024,2025,2026"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F115:F122 F103:F113 F91:F101 F79:F89 F67:F77 F55:F65 F43:F53 F31:F41 F21:F29 F12:F19 F3:F10 L115:L122 L103:L113 L91:L101 L79:L89 L67:L77 L55:L65 L43:L53 L31:L41 L21:L29 L12:L19 L3:L10 R115:R122 R103:R113 R91:R101 R79:R89 R67:R77 R55:R65 R43:R53 R31:R41 R21:R29 R12:R19 R3:R10" xr:uid="{4D9D45E0-ADCE-4751-8C9C-48678D222CFF}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
